--- a/measurements/32/Filled_2D_sections/coronal/week32_coronal_Batch_Allmarks.xlsx
+++ b/measurements/32/Filled_2D_sections/coronal/week32_coronal_Batch_Allmarks.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O24"/>
+  <dimension ref="A1:AH29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -487,12 +487,107 @@
           <t>mean_depth_mm</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Primary_count</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>Primary_v1_mm</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>Primary_v2_mm</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>Primary_v3_mm</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>Secondary_count</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>Secondary_v1_mm</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>Secondary_v2_mm</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>Secondary_v3_mm</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>Secondary_min_mm</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>Secondary_max_mm</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>Secondary_mean_mm</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>Tertiary_count</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>Tertiary_v1_mm</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Tertiary_v2_mm</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>Tertiary_v3_mm</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>Tertiary_min_mm</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>Tertiary_max_mm</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>Tertiary_mean_mm</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>Unclassified_count</t>
+        </is>
+      </c>
+      <c r="AG1" t="inlineStr">
         <is>
           <t>Metric</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="AH1" t="inlineStr">
         <is>
           <t>Mean</t>
         </is>
@@ -506,17 +601,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>coronal</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>6.745687091017252</v>
+        <v>2571.315192743764</v>
       </c>
       <c r="D2" t="n">
-        <v>16.29261060749612</v>
+        <v>318.0938261463529</v>
       </c>
       <c r="E2" t="n">
-        <v>11.45234743269478</v>
+        <v>223.593449876422</v>
       </c>
       <c r="F2" t="n">
         <v>1.42264375956523</v>
@@ -525,24 +620,60 @@
         <v>0.3193410139406404</v>
       </c>
       <c r="H2" t="n">
+        <v>10</v>
+      </c>
+      <c r="I2" t="n">
+        <v>1.30766369047619</v>
+      </c>
+      <c r="J2" t="n">
+        <v>20.17857142857143</v>
+      </c>
+      <c r="K2" t="n">
+        <v>5.944196428571428</v>
+      </c>
+      <c r="L2" t="n">
         <v>2</v>
       </c>
-      <c r="I2" t="n">
-        <v>0.6287157012195123</v>
-      </c>
-      <c r="J2" t="n">
-        <v>1.033536585365854</v>
-      </c>
-      <c r="K2" t="n">
-        <v>0.8311261432926831</v>
-      </c>
-      <c r="N2" t="inlineStr">
+      <c r="M2" t="n">
+        <v>20.17857142857143</v>
+      </c>
+      <c r="N2" t="n">
+        <v>12.27492559523809</v>
+      </c>
+      <c r="P2" t="n">
+        <v>4</v>
+      </c>
+      <c r="T2" t="n">
+        <v>3.515625</v>
+      </c>
+      <c r="U2" t="n">
+        <v>7.743675595238095</v>
+      </c>
+      <c r="V2" t="n">
+        <v>4.793526785714285</v>
+      </c>
+      <c r="W2" t="n">
+        <v>4</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>1.30766369047619</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>2.857142857142857</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>1.953590029761905</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG2" t="inlineStr">
         <is>
           <t>area</t>
         </is>
       </c>
-      <c r="O2" s="2" t="n">
-        <v>6.638726948245093</v>
+      <c r="AH2" s="2" t="n">
+        <v>2530.544217687075</v>
       </c>
     </row>
     <row r="3">
@@ -553,43 +684,79 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>coronal</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>6.770969660916122</v>
+        <v>2580.952380952381</v>
       </c>
       <c r="D3" t="n">
-        <v>16.33547302571739</v>
+        <v>318.9306638354346</v>
       </c>
       <c r="E3" t="n">
-        <v>11.48684045454351</v>
+        <v>224.2668850648971</v>
       </c>
       <c r="F3" t="n">
         <v>1.42210323982136</v>
       </c>
       <c r="G3" t="n">
-        <v>0.3188579885904241</v>
+        <v>0.3188579885904242</v>
       </c>
       <c r="H3" t="n">
+        <v>9</v>
+      </c>
+      <c r="I3" t="n">
+        <v>1.063988095238095</v>
+      </c>
+      <c r="J3" t="n">
+        <v>20.15997023809524</v>
+      </c>
+      <c r="K3" t="n">
+        <v>6.483134920634921</v>
+      </c>
+      <c r="L3" t="n">
         <v>2</v>
       </c>
-      <c r="I3" t="n">
-        <v>0.6189024390243902</v>
-      </c>
-      <c r="J3" t="n">
-        <v>1.032583841463415</v>
-      </c>
-      <c r="K3" t="n">
-        <v>0.8257431402439025</v>
-      </c>
-      <c r="N3" t="inlineStr">
+      <c r="M3" t="n">
+        <v>20.15997023809524</v>
+      </c>
+      <c r="N3" t="n">
+        <v>12.08333333333333</v>
+      </c>
+      <c r="P3" t="n">
+        <v>4</v>
+      </c>
+      <c r="T3" t="n">
+        <v>3.484002976190476</v>
+      </c>
+      <c r="U3" t="n">
+        <v>7.743675595238095</v>
+      </c>
+      <c r="V3" t="n">
+        <v>4.796316964285714</v>
+      </c>
+      <c r="W3" t="n">
+        <v>3</v>
+      </c>
+      <c r="X3" t="n">
+        <v>3.333333333333333</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>2.522321428571428</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>1.063988095238095</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="inlineStr">
         <is>
           <t>perimeter</t>
         </is>
       </c>
-      <c r="O3" s="2" t="n">
-        <v>15.86980501965779</v>
+      <c r="AH3" s="2" t="n">
+        <v>309.8390503837949</v>
       </c>
     </row>
     <row r="4">
@@ -600,17 +767,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>coronal</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>6.75609756097561</v>
+        <v>2575.283446712018</v>
       </c>
       <c r="D4" t="n">
-        <v>15.96543469370865</v>
+        <v>311.7061059247879</v>
       </c>
       <c r="E4" t="n">
-        <v>11.50357927345648</v>
+        <v>224.5936905770075</v>
       </c>
       <c r="F4" t="n">
         <v>1.387866707760038</v>
@@ -619,24 +786,60 @@
         <v>0.3330767213894454</v>
       </c>
       <c r="H4" t="n">
+        <v>8</v>
+      </c>
+      <c r="I4" t="n">
+        <v>2.4609375</v>
+      </c>
+      <c r="J4" t="n">
+        <v>19.52380952380952</v>
+      </c>
+      <c r="K4" t="n">
+        <v>7.075427827380952</v>
+      </c>
+      <c r="L4" t="n">
         <v>2</v>
       </c>
-      <c r="I4" t="n">
-        <v>0.6282393292682927</v>
-      </c>
-      <c r="J4" t="n">
-        <v>1</v>
-      </c>
-      <c r="K4" t="n">
-        <v>0.8141196646341464</v>
-      </c>
-      <c r="N4" t="inlineStr">
+      <c r="M4" t="n">
+        <v>19.52380952380952</v>
+      </c>
+      <c r="N4" t="n">
+        <v>12.265625</v>
+      </c>
+      <c r="P4" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>7.743675595238095</v>
+      </c>
+      <c r="R4" t="n">
+        <v>4.285714285714286</v>
+      </c>
+      <c r="S4" t="n">
+        <v>3.833705357142857</v>
+      </c>
+      <c r="W4" t="n">
+        <v>3</v>
+      </c>
+      <c r="X4" t="n">
+        <v>3.37797619047619</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>3.111979166666667</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>2.4609375</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="inlineStr">
         <is>
           <t>perimeter_convex</t>
         </is>
       </c>
-      <c r="O4" s="2" t="n">
-        <v>11.54853041550008</v>
+      <c r="AH4" s="2" t="n">
+        <v>225.4713081121445</v>
       </c>
     </row>
     <row r="5">
@@ -647,42 +850,81 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>coronal</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>6.721594289113623</v>
+        <v>2562.131519274376</v>
       </c>
       <c r="D5" t="n">
-        <v>17.45252155676121</v>
+        <v>340.7397065843854</v>
       </c>
       <c r="E5" t="n">
-        <v>11.55582646916552</v>
+        <v>225.613754874184</v>
       </c>
       <c r="F5" t="n">
         <v>1.510278957833944</v>
       </c>
       <c r="G5" t="n">
-        <v>0.2773101674108493</v>
+        <v>0.2773101674108494</v>
       </c>
       <c r="H5" t="n">
+        <v>10</v>
+      </c>
+      <c r="I5" t="n">
+        <v>1.638764880952381</v>
+      </c>
+      <c r="J5" t="n">
+        <v>19.04761904761905</v>
+      </c>
+      <c r="K5" t="n">
+        <v>7.064546130952381</v>
+      </c>
+      <c r="L5" t="n">
         <v>3</v>
       </c>
-      <c r="I5" t="n">
-        <v>0.6266196646341463</v>
-      </c>
-      <c r="J5" t="n">
-        <v>0.975609756097561</v>
-      </c>
-      <c r="K5" t="n">
-        <v>0.7942390752032521</v>
-      </c>
-      <c r="N5" t="inlineStr">
+      <c r="M5" t="n">
+        <v>19.04761904761905</v>
+      </c>
+      <c r="N5" t="n">
+        <v>15.23809523809524</v>
+      </c>
+      <c r="O5" t="n">
+        <v>12.23400297619048</v>
+      </c>
+      <c r="P5" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>7.327008928571428</v>
+      </c>
+      <c r="R5" t="n">
+        <v>4.265252976190476</v>
+      </c>
+      <c r="S5" t="n">
+        <v>3.407738095238095</v>
+      </c>
+      <c r="W5" t="n">
+        <v>4</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>1.638764880952381</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>2.976190476190476</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>2.281436011904762</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="inlineStr">
         <is>
           <t>LGI</t>
         </is>
       </c>
-      <c r="O5" s="2" t="n">
+      <c r="AH5" s="2" t="n">
         <v>1.374013985534746</v>
       </c>
     </row>
@@ -694,17 +936,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>coronal</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>6.708804283164783</v>
+        <v>2557.256235827664</v>
       </c>
       <c r="D6" t="n">
-        <v>17.65702827093078</v>
+        <v>344.7324567181723</v>
       </c>
       <c r="E6" t="n">
-        <v>11.57603199016757</v>
+        <v>226.0082436175573</v>
       </c>
       <c r="F6" t="n">
         <v>1.525309215275862</v>
@@ -713,23 +955,62 @@
         <v>0.2704081404558287</v>
       </c>
       <c r="H6" t="n">
+        <v>10</v>
+      </c>
+      <c r="I6" t="n">
+        <v>2.113095238095238</v>
+      </c>
+      <c r="J6" t="n">
+        <v>18.93787202380952</v>
+      </c>
+      <c r="K6" t="n">
+        <v>7.691220238095238</v>
+      </c>
+      <c r="L6" t="n">
         <v>3</v>
       </c>
-      <c r="I6" t="n">
-        <v>0.6343368902439025</v>
-      </c>
-      <c r="J6" t="n">
-        <v>0.9699885670731707</v>
-      </c>
-      <c r="K6" t="n">
-        <v>0.7949377540650406</v>
-      </c>
-      <c r="N6" t="inlineStr">
+      <c r="M6" t="n">
+        <v>18.93787202380952</v>
+      </c>
+      <c r="N6" t="n">
+        <v>15.23809523809524</v>
+      </c>
+      <c r="O6" t="n">
+        <v>12.38467261904762</v>
+      </c>
+      <c r="P6" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>8.240327380952381</v>
+      </c>
+      <c r="R6" t="n">
+        <v>7.639508928571428</v>
+      </c>
+      <c r="S6" t="n">
+        <v>3.720238095238095</v>
+      </c>
+      <c r="W6" t="n">
+        <v>4</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>2.113095238095238</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>3.069196428571428</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>2.687872023809524</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="inlineStr">
         <is>
           <t>Compactness</t>
         </is>
       </c>
-      <c r="O6" s="2" t="n">
+      <c r="AH6" s="2" t="n">
         <v>0.3350900967180895</v>
       </c>
     </row>
@@ -741,43 +1022,82 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>coronal</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>6.616299821534801</v>
+        <v>2521.995464852608</v>
       </c>
       <c r="D7" t="n">
-        <v>17.02879996125291</v>
+        <v>332.4670468625568</v>
       </c>
       <c r="E7" t="n">
-        <v>11.60215559529095</v>
+        <v>226.5182759080614</v>
       </c>
       <c r="F7" t="n">
         <v>1.467727253042918</v>
       </c>
       <c r="G7" t="n">
-        <v>0.2867193171614328</v>
+        <v>0.2867193171614329</v>
       </c>
       <c r="H7" t="n">
+        <v>11</v>
+      </c>
+      <c r="I7" t="n">
+        <v>2.661830357142857</v>
+      </c>
+      <c r="J7" t="n">
+        <v>16.45647321428571</v>
+      </c>
+      <c r="K7" t="n">
+        <v>6.871617965367966</v>
+      </c>
+      <c r="L7" t="n">
         <v>3</v>
       </c>
-      <c r="I7" t="n">
-        <v>0.6411013719512195</v>
-      </c>
-      <c r="J7" t="n">
-        <v>0.8428925304878049</v>
-      </c>
-      <c r="K7" t="n">
-        <v>0.7385670731707318</v>
-      </c>
-      <c r="N7" t="inlineStr">
+      <c r="M7" t="n">
+        <v>16.45647321428571</v>
+      </c>
+      <c r="N7" t="n">
+        <v>14.28571428571428</v>
+      </c>
+      <c r="O7" t="n">
+        <v>12.51674107142857</v>
+      </c>
+      <c r="P7" t="n">
+        <v>5</v>
+      </c>
+      <c r="T7" t="n">
+        <v>3.465401785714286</v>
+      </c>
+      <c r="U7" t="n">
+        <v>8.699776785714285</v>
+      </c>
+      <c r="V7" t="n">
+        <v>4.749627976190476</v>
+      </c>
+      <c r="W7" t="n">
+        <v>3</v>
+      </c>
+      <c r="X7" t="n">
+        <v>2.974330357142857</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>2.944568452380952</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>2.661830357142857</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="inlineStr">
         <is>
           <t>Sulci_count</t>
         </is>
       </c>
-      <c r="O7" s="2" t="n">
-        <v>2.25</v>
+      <c r="AH7" s="2" t="n">
+        <v>9.199999999999999</v>
       </c>
     </row>
     <row r="8">
@@ -788,17 +1108,17 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>coronal</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>6.566627007733493</v>
+        <v>2503.061224489796</v>
       </c>
       <c r="D8" t="n">
-        <v>17.75805595153716</v>
+        <v>346.7049019109635</v>
       </c>
       <c r="E8" t="n">
-        <v>11.64501800478959</v>
+        <v>227.3551134268443</v>
       </c>
       <c r="F8" t="n">
         <v>1.52494877588281</v>
@@ -807,24 +1127,63 @@
         <v>0.2616744816400987</v>
       </c>
       <c r="H8" t="n">
+        <v>11</v>
+      </c>
+      <c r="I8" t="n">
+        <v>1.919642857142857</v>
+      </c>
+      <c r="J8" t="n">
+        <v>15.83519345238095</v>
+      </c>
+      <c r="K8" t="n">
+        <v>7.216585497835498</v>
+      </c>
+      <c r="L8" t="n">
         <v>3</v>
       </c>
-      <c r="I8" t="n">
-        <v>0.6189977134146342</v>
-      </c>
-      <c r="J8" t="n">
-        <v>0.8110708841463415</v>
-      </c>
-      <c r="K8" t="n">
-        <v>0.7124618902439025</v>
-      </c>
-      <c r="N8" t="inlineStr">
+      <c r="M8" t="n">
+        <v>15.83519345238095</v>
+      </c>
+      <c r="N8" t="n">
+        <v>13.80952380952381</v>
+      </c>
+      <c r="O8" t="n">
+        <v>12.08519345238095</v>
+      </c>
+      <c r="P8" t="n">
+        <v>5</v>
+      </c>
+      <c r="T8" t="n">
+        <v>3.322172619047619</v>
+      </c>
+      <c r="U8" t="n">
+        <v>9.047619047619047</v>
+      </c>
+      <c r="V8" t="n">
+        <v>5.942708333333333</v>
+      </c>
+      <c r="W8" t="n">
+        <v>3</v>
+      </c>
+      <c r="X8" t="n">
+        <v>3.125</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>2.894345238095238</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>1.919642857142857</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="inlineStr">
         <is>
           <t>min_depth_mm</t>
         </is>
       </c>
-      <c r="O8" s="2" t="n">
-        <v>0.6304020579268294</v>
+      <c r="AH8" s="2" t="n">
+        <v>1.615606398809524</v>
       </c>
     </row>
     <row r="9">
@@ -835,43 +1194,79 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>coronal</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>6.589827483640691</v>
+        <v>2511.904761904762</v>
       </c>
       <c r="D9" t="n">
-        <v>16.85633491597525</v>
+        <v>329.0998721690405</v>
       </c>
       <c r="E9" t="n">
-        <v>11.63073053883343</v>
+        <v>227.0761676629384</v>
       </c>
       <c r="F9" t="n">
         <v>1.449292876289604</v>
       </c>
       <c r="G9" t="n">
-        <v>0.2914456690933672</v>
+        <v>0.2914456690933673</v>
       </c>
       <c r="H9" t="n">
+        <v>10</v>
+      </c>
+      <c r="I9" t="n">
+        <v>1.821056547619047</v>
+      </c>
+      <c r="J9" t="n">
+        <v>16.15699404761905</v>
+      </c>
+      <c r="K9" t="n">
+        <v>7.045200892857143</v>
+      </c>
+      <c r="L9" t="n">
         <v>2</v>
       </c>
-      <c r="I9" t="n">
-        <v>0.6400533536585367</v>
-      </c>
-      <c r="J9" t="n">
-        <v>0.8275533536585367</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0.7338033536585367</v>
-      </c>
-      <c r="N9" t="inlineStr">
+      <c r="M9" t="n">
+        <v>16.15699404761905</v>
+      </c>
+      <c r="N9" t="n">
+        <v>12.49627976190476</v>
+      </c>
+      <c r="P9" t="n">
+        <v>5</v>
+      </c>
+      <c r="T9" t="n">
+        <v>4.633556547619047</v>
+      </c>
+      <c r="U9" t="n">
+        <v>8.571428571428571</v>
+      </c>
+      <c r="V9" t="n">
+        <v>6.959449404761903</v>
+      </c>
+      <c r="W9" t="n">
+        <v>3</v>
+      </c>
+      <c r="X9" t="n">
+        <v>2.992931547619047</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>2.1875</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>1.821056547619047</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="inlineStr">
         <is>
           <t>max_depth_mm</t>
         </is>
       </c>
-      <c r="O9" s="2" t="n">
-        <v>0.8620760289634146</v>
+      <c r="AH9" s="2" t="n">
+        <v>16.83100818452381</v>
       </c>
     </row>
     <row r="10">
@@ -882,17 +1277,17 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>coronal</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>6.624925639500297</v>
+        <v>2525.283446712018</v>
       </c>
       <c r="D10" t="n">
-        <v>16.19014694051045</v>
+        <v>316.0933450290135</v>
       </c>
       <c r="E10" t="n">
-        <v>11.65338744477528</v>
+        <v>227.5185167789459</v>
       </c>
       <c r="F10" t="n">
         <v>1.38930821765213</v>
@@ -901,24 +1296,60 @@
         <v>0.3176064336426134</v>
       </c>
       <c r="H10" t="n">
+        <v>11</v>
+      </c>
+      <c r="I10" t="n">
+        <v>1.063988095238095</v>
+      </c>
+      <c r="J10" t="n">
+        <v>14.89583333333333</v>
+      </c>
+      <c r="K10" t="n">
+        <v>5.785477543290042</v>
+      </c>
+      <c r="L10" t="n">
         <v>2</v>
       </c>
-      <c r="I10" t="n">
-        <v>0.6163300304878049</v>
-      </c>
-      <c r="J10" t="n">
-        <v>0.7629573170731707</v>
-      </c>
-      <c r="K10" t="n">
-        <v>0.6896436737804879</v>
-      </c>
-      <c r="N10" t="inlineStr">
+      <c r="M10" t="n">
+        <v>14.89583333333333</v>
+      </c>
+      <c r="N10" t="n">
+        <v>12.03311011904762</v>
+      </c>
+      <c r="P10" t="n">
+        <v>5</v>
+      </c>
+      <c r="T10" t="n">
+        <v>4.202008928571428</v>
+      </c>
+      <c r="U10" t="n">
+        <v>9.019717261904761</v>
+      </c>
+      <c r="V10" t="n">
+        <v>6.105282738095237</v>
+      </c>
+      <c r="W10" t="n">
+        <v>4</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>1.063988095238095</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>2.241443452380952</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>1.546223958333333</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="inlineStr">
         <is>
           <t>mean_depth_mm</t>
         </is>
       </c>
-      <c r="O10" s="2" t="n">
-        <v>0.7439453125000001</v>
+      <c r="AH10" s="2" t="n">
+        <v>6.680225830665283</v>
       </c>
     </row>
     <row r="11">
@@ -929,17 +1360,17 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>coronal</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>6.685901249256395</v>
+        <v>2548.526077097506</v>
       </c>
       <c r="D11" t="n">
-        <v>15.50620470395902</v>
+        <v>302.7401870772952</v>
       </c>
       <c r="E11" t="n">
-        <v>11.57848332858667</v>
+        <v>226.0561030819302</v>
       </c>
       <c r="F11" t="n">
         <v>1.339225895474152</v>
@@ -948,16 +1379,60 @@
         <v>0.3494288797143514</v>
       </c>
       <c r="H11" t="n">
+        <v>10</v>
+      </c>
+      <c r="I11" t="n">
+        <v>1.376488095238095</v>
+      </c>
+      <c r="J11" t="n">
+        <v>15.34412202380952</v>
+      </c>
+      <c r="K11" t="n">
+        <v>5.866443452380953</v>
+      </c>
+      <c r="L11" t="n">
         <v>2</v>
       </c>
-      <c r="I11" t="n">
-        <v>0.5456364329268293</v>
-      </c>
-      <c r="J11" t="n">
-        <v>0.7859184451219512</v>
-      </c>
-      <c r="K11" t="n">
-        <v>0.6657774390243902</v>
+      <c r="M11" t="n">
+        <v>15.34412202380952</v>
+      </c>
+      <c r="N11" t="n">
+        <v>10.65290178571428</v>
+      </c>
+      <c r="P11" t="n">
+        <v>5</v>
+      </c>
+      <c r="T11" t="n">
+        <v>3.634672619047619</v>
+      </c>
+      <c r="U11" t="n">
+        <v>8.986235119047619</v>
+      </c>
+      <c r="V11" t="n">
+        <v>5.59672619047619</v>
+      </c>
+      <c r="W11" t="n">
+        <v>3</v>
+      </c>
+      <c r="X11" t="n">
+        <v>1.7578125</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>1.549479166666667</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>1.376488095238095</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="inlineStr">
+        <is>
+          <t>Primary_count</t>
+        </is>
+      </c>
+      <c r="AH11" s="2" t="n">
+        <v>2.25</v>
       </c>
     </row>
     <row r="12">
@@ -968,17 +1443,17 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>coronal</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>6.747769185008924</v>
+        <v>2572.108843537415</v>
       </c>
       <c r="D12" t="n">
-        <v>15.39680761825748</v>
+        <v>300.6043392135983</v>
       </c>
       <c r="E12" t="n">
-        <v>11.52970283787425</v>
+        <v>225.103722072783</v>
       </c>
       <c r="F12" t="n">
         <v>1.335403681669927</v>
@@ -987,16 +1462,60 @@
         <v>0.3576915791283737</v>
       </c>
       <c r="H12" t="n">
+        <v>9</v>
+      </c>
+      <c r="I12" t="n">
+        <v>1.104910714285714</v>
+      </c>
+      <c r="J12" t="n">
+        <v>15.72358630952381</v>
+      </c>
+      <c r="K12" t="n">
+        <v>6.342592592592592</v>
+      </c>
+      <c r="L12" t="n">
         <v>2</v>
       </c>
-      <c r="I12" t="n">
-        <v>0.6186166158536586</v>
-      </c>
-      <c r="J12" t="n">
-        <v>0.8053544207317074</v>
-      </c>
-      <c r="K12" t="n">
-        <v>0.711985518292683</v>
+      <c r="M12" t="n">
+        <v>15.72358630952381</v>
+      </c>
+      <c r="N12" t="n">
+        <v>12.07775297619048</v>
+      </c>
+      <c r="P12" t="n">
+        <v>4</v>
+      </c>
+      <c r="T12" t="n">
+        <v>4.428943452380953</v>
+      </c>
+      <c r="U12" t="n">
+        <v>8.844866071428571</v>
+      </c>
+      <c r="V12" t="n">
+        <v>5.922154017857143</v>
+      </c>
+      <c r="W12" t="n">
+        <v>3</v>
+      </c>
+      <c r="X12" t="n">
+        <v>2.291666666666667</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>2.196800595238095</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>1.104910714285714</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="inlineStr">
+        <is>
+          <t>Primary_v1_mm</t>
+        </is>
+      </c>
+      <c r="AH12" s="2" t="n">
+        <v>16.83100818452381</v>
       </c>
     </row>
     <row r="13">
@@ -1007,35 +1526,82 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>coronal</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>6.722784057108864</v>
+        <v>2562.585034013605</v>
       </c>
       <c r="D13" t="n">
-        <v>16.19750096739792</v>
+        <v>316.2369236491975</v>
       </c>
       <c r="E13" t="n">
-        <v>11.54990837632156</v>
+        <v>225.4982111567543</v>
       </c>
       <c r="F13" t="n">
         <v>1.402392161015267</v>
       </c>
       <c r="G13" t="n">
-        <v>0.3220052825255653</v>
+        <v>0.3220052825255652</v>
       </c>
       <c r="H13" t="n">
+        <v>9</v>
+      </c>
+      <c r="I13" t="n">
+        <v>0.9951636904761905</v>
+      </c>
+      <c r="J13" t="n">
+        <v>15.34412202380952</v>
+      </c>
+      <c r="K13" t="n">
+        <v>6.958912037037036</v>
+      </c>
+      <c r="L13" t="n">
         <v>3</v>
       </c>
-      <c r="I13" t="n">
-        <v>0.6070884146341463</v>
-      </c>
-      <c r="J13" t="n">
-        <v>0.7859184451219512</v>
-      </c>
-      <c r="K13" t="n">
-        <v>0.6707317073170732</v>
+      <c r="M13" t="n">
+        <v>15.34412202380952</v>
+      </c>
+      <c r="N13" t="n">
+        <v>12.08891369047619</v>
+      </c>
+      <c r="O13" t="n">
+        <v>11.85267857142857</v>
+      </c>
+      <c r="P13" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>8.727678571428571</v>
+      </c>
+      <c r="R13" t="n">
+        <v>4.518229166666666</v>
+      </c>
+      <c r="S13" t="n">
+        <v>4.425223214285714</v>
+      </c>
+      <c r="W13" t="n">
+        <v>3</v>
+      </c>
+      <c r="X13" t="n">
+        <v>3.210565476190476</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>1.467633928571428</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>0.9951636904761905</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="inlineStr">
+        <is>
+          <t>Primary_v2_mm</t>
+        </is>
+      </c>
+      <c r="AH13" s="2" t="n">
+        <v>12.78720238095238</v>
       </c>
     </row>
     <row r="14">
@@ -1046,35 +1612,76 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>coronal</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>6.713563355145747</v>
+        <v>2559.07029478458</v>
       </c>
       <c r="D14" t="n">
-        <v>15.33517562470785</v>
+        <v>299.4010479109627</v>
       </c>
       <c r="E14" t="n">
-        <v>11.57848335475456</v>
+        <v>226.0561035928272</v>
       </c>
       <c r="F14" t="n">
         <v>1.32445460729627</v>
       </c>
       <c r="G14" t="n">
-        <v>0.3587446619324931</v>
+        <v>0.3587446619324932</v>
       </c>
       <c r="H14" t="n">
+        <v>9</v>
+      </c>
+      <c r="I14" t="n">
+        <v>1.441592261904762</v>
+      </c>
+      <c r="J14" t="n">
+        <v>15.29017857142857</v>
+      </c>
+      <c r="K14" t="n">
+        <v>6.557746362433862</v>
+      </c>
+      <c r="L14" t="n">
         <v>2</v>
       </c>
-      <c r="I14" t="n">
-        <v>0.6366234756097561</v>
-      </c>
-      <c r="J14" t="n">
-        <v>0.7831554878048781</v>
-      </c>
-      <c r="K14" t="n">
-        <v>0.7098894817073171</v>
+      <c r="M14" t="n">
+        <v>15.29017857142857</v>
+      </c>
+      <c r="N14" t="n">
+        <v>12.42931547619048</v>
+      </c>
+      <c r="P14" t="n">
+        <v>5</v>
+      </c>
+      <c r="T14" t="n">
+        <v>3.392857142857143</v>
+      </c>
+      <c r="U14" t="n">
+        <v>8.822544642857142</v>
+      </c>
+      <c r="V14" t="n">
+        <v>5.675595238095238</v>
+      </c>
+      <c r="W14" t="n">
+        <v>2</v>
+      </c>
+      <c r="X14" t="n">
+        <v>1.480654761904762</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>1.441592261904762</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="inlineStr">
+        <is>
+          <t>Primary_v3_mm</t>
+        </is>
+      </c>
+      <c r="AH14" s="2" t="n">
+        <v>12.21465773809524</v>
       </c>
     </row>
     <row r="15">
@@ -1085,17 +1692,17 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>coronal</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>6.701368233194527</v>
+        <v>2554.421768707483</v>
       </c>
       <c r="D15" t="n">
-        <v>15.08535514226774</v>
+        <v>294.5236003966559</v>
       </c>
       <c r="E15" t="n">
-        <v>11.65338742151493</v>
+        <v>227.5185163248153</v>
       </c>
       <c r="F15" t="n">
         <v>1.294503872274647</v>
@@ -1104,16 +1711,60 @@
         <v>0.3700515851544841</v>
       </c>
       <c r="H15" t="n">
+        <v>9</v>
+      </c>
+      <c r="I15" t="n">
+        <v>1.824776785714286</v>
+      </c>
+      <c r="J15" t="n">
+        <v>15.3031994047619</v>
+      </c>
+      <c r="K15" t="n">
+        <v>6.433325066137566</v>
+      </c>
+      <c r="L15" t="n">
         <v>2</v>
       </c>
-      <c r="I15" t="n">
-        <v>0.6427210365853658</v>
-      </c>
-      <c r="J15" t="n">
-        <v>0.7838224085365854</v>
-      </c>
-      <c r="K15" t="n">
-        <v>0.7132717225609756</v>
+      <c r="M15" t="n">
+        <v>15.3031994047619</v>
+      </c>
+      <c r="N15" t="n">
+        <v>12.54836309523809</v>
+      </c>
+      <c r="P15" t="n">
+        <v>4</v>
+      </c>
+      <c r="T15" t="n">
+        <v>4.680059523809524</v>
+      </c>
+      <c r="U15" t="n">
+        <v>8.755580357142856</v>
+      </c>
+      <c r="V15" t="n">
+        <v>5.904947916666666</v>
+      </c>
+      <c r="W15" t="n">
+        <v>3</v>
+      </c>
+      <c r="X15" t="n">
+        <v>2.704613095238095</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>1.899181547619047</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>1.824776785714286</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="inlineStr">
+        <is>
+          <t>Secondary_count</t>
+        </is>
+      </c>
+      <c r="AH15" s="2" t="n">
+        <v>4.2</v>
       </c>
     </row>
     <row r="16">
@@ -1124,17 +1775,17 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>coronal</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>6.660618679357525</v>
+        <v>2538.888888888889</v>
       </c>
       <c r="D16" t="n">
-        <v>14.98187610870454</v>
+        <v>292.5032954556601</v>
       </c>
       <c r="E16" t="n">
-        <v>11.59277082943335</v>
+        <v>226.335049527032</v>
       </c>
       <c r="F16" t="n">
         <v>1.292346439788705</v>
@@ -1143,16 +1794,57 @@
         <v>0.3728996985126125</v>
       </c>
       <c r="H16" t="n">
+        <v>8</v>
+      </c>
+      <c r="I16" t="n">
+        <v>1.793154761904762</v>
+      </c>
+      <c r="J16" t="n">
+        <v>15.44456845238095</v>
+      </c>
+      <c r="K16" t="n">
+        <v>6.821289062499999</v>
+      </c>
+      <c r="L16" t="n">
         <v>2</v>
       </c>
-      <c r="I16" t="n">
-        <v>0.6433879573170732</v>
-      </c>
-      <c r="J16" t="n">
-        <v>0.791063262195122</v>
-      </c>
-      <c r="K16" t="n">
-        <v>0.7172256097560976</v>
+      <c r="M16" t="n">
+        <v>15.44456845238095</v>
+      </c>
+      <c r="N16" t="n">
+        <v>12.56138392857143</v>
+      </c>
+      <c r="P16" t="n">
+        <v>4</v>
+      </c>
+      <c r="T16" t="n">
+        <v>4.419642857142857</v>
+      </c>
+      <c r="U16" t="n">
+        <v>8.746279761904761</v>
+      </c>
+      <c r="V16" t="n">
+        <v>5.644996279761904</v>
+      </c>
+      <c r="W16" t="n">
+        <v>2</v>
+      </c>
+      <c r="X16" t="n">
+        <v>2.191220238095238</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>1.793154761904762</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="inlineStr">
+        <is>
+          <t>Secondary_v1_mm</t>
+        </is>
+      </c>
+      <c r="AH16" s="2" t="n">
+        <v>8.009672619047619</v>
       </c>
     </row>
     <row r="17">
@@ -1163,17 +1855,17 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>coronal</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>6.617787031528852</v>
+        <v>2522.562358276644</v>
       </c>
       <c r="D17" t="n">
-        <v>14.73450693851564</v>
+        <v>287.6737068948291</v>
       </c>
       <c r="E17" t="n">
-        <v>11.56664722140242</v>
+        <v>225.8250171797616</v>
       </c>
       <c r="F17" t="n">
         <v>1.273878822140572</v>
@@ -1182,16 +1874,57 @@
         <v>0.3830464446909048</v>
       </c>
       <c r="H17" t="n">
+        <v>8</v>
+      </c>
+      <c r="I17" t="n">
+        <v>1.300223214285714</v>
+      </c>
+      <c r="J17" t="n">
+        <v>16.04352678571428</v>
+      </c>
+      <c r="K17" t="n">
+        <v>6.800362723214284</v>
+      </c>
+      <c r="L17" t="n">
         <v>2</v>
       </c>
-      <c r="I17" t="n">
-        <v>0.6585365853658537</v>
-      </c>
-      <c r="J17" t="n">
-        <v>0.8217416158536586</v>
-      </c>
-      <c r="K17" t="n">
-        <v>0.7401391006097562</v>
+      <c r="M17" t="n">
+        <v>16.04352678571428</v>
+      </c>
+      <c r="N17" t="n">
+        <v>12.85714285714286</v>
+      </c>
+      <c r="P17" t="n">
+        <v>4</v>
+      </c>
+      <c r="T17" t="n">
+        <v>3.902529761904762</v>
+      </c>
+      <c r="U17" t="n">
+        <v>8.433779761904761</v>
+      </c>
+      <c r="V17" t="n">
+        <v>5.394345238095238</v>
+      </c>
+      <c r="W17" t="n">
+        <v>2</v>
+      </c>
+      <c r="X17" t="n">
+        <v>2.624627976190476</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>1.300223214285714</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="inlineStr">
+        <is>
+          <t>Secondary_v2_mm</t>
+        </is>
+      </c>
+      <c r="AH17" s="2" t="n">
+        <v>5.177176339285714</v>
       </c>
     </row>
     <row r="18">
@@ -1202,35 +1935,76 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>coronal</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>6.6017251635931</v>
+        <v>2516.439909297052</v>
       </c>
       <c r="D18" t="n">
-        <v>14.69756258697045</v>
+        <v>286.9524124122801</v>
       </c>
       <c r="E18" t="n">
-        <v>11.52378478864344</v>
+        <v>224.9881792068481</v>
       </c>
       <c r="F18" t="n">
         <v>1.275411061256084</v>
       </c>
       <c r="G18" t="n">
-        <v>0.3840401828678623</v>
+        <v>0.3840401828678624</v>
       </c>
       <c r="H18" t="n">
+        <v>8</v>
+      </c>
+      <c r="I18" t="n">
+        <v>1.177455357142857</v>
+      </c>
+      <c r="J18" t="n">
+        <v>16.51971726190476</v>
+      </c>
+      <c r="K18" t="n">
+        <v>6.646205357142857</v>
+      </c>
+      <c r="L18" t="n">
         <v>2</v>
       </c>
-      <c r="I18" t="n">
-        <v>0.6585365853658537</v>
-      </c>
-      <c r="J18" t="n">
-        <v>0.8461318597560976</v>
-      </c>
-      <c r="K18" t="n">
-        <v>0.7523342225609757</v>
+      <c r="M18" t="n">
+        <v>16.51971726190476</v>
+      </c>
+      <c r="N18" t="n">
+        <v>12.85714285714286</v>
+      </c>
+      <c r="P18" t="n">
+        <v>4</v>
+      </c>
+      <c r="T18" t="n">
+        <v>3.638392857142857</v>
+      </c>
+      <c r="U18" t="n">
+        <v>7.9296875</v>
+      </c>
+      <c r="V18" t="n">
+        <v>4.934430803571429</v>
+      </c>
+      <c r="W18" t="n">
+        <v>2</v>
+      </c>
+      <c r="X18" t="n">
+        <v>2.877604166666667</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>1.177455357142857</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="inlineStr">
+        <is>
+          <t>Secondary_v3_mm</t>
+        </is>
+      </c>
+      <c r="AH18" s="2" t="n">
+        <v>3.84672619047619</v>
       </c>
     </row>
     <row r="19">
@@ -1241,17 +2015,17 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>coronal</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>6.508923259964307</v>
+        <v>2481.065759637188</v>
       </c>
       <c r="D19" t="n">
-        <v>14.41324908558915</v>
+        <v>281.4015297662644</v>
       </c>
       <c r="E19" t="n">
-        <v>11.52133345313189</v>
+        <v>224.9403197992416</v>
       </c>
       <c r="F19" t="n">
         <v>1.251005288946927</v>
@@ -1260,16 +2034,57 @@
         <v>0.3937270303097075</v>
       </c>
       <c r="H19" t="n">
+        <v>8</v>
+      </c>
+      <c r="I19" t="n">
+        <v>1.489955357142857</v>
+      </c>
+      <c r="J19" t="n">
+        <v>16.49739583333333</v>
+      </c>
+      <c r="K19" t="n">
+        <v>6.449032738095237</v>
+      </c>
+      <c r="L19" t="n">
         <v>2</v>
       </c>
-      <c r="I19" t="n">
-        <v>0.6585365853658537</v>
-      </c>
-      <c r="J19" t="n">
-        <v>0.8449885670731707</v>
-      </c>
-      <c r="K19" t="n">
-        <v>0.7517625762195121</v>
+      <c r="M19" t="n">
+        <v>16.49739583333333</v>
+      </c>
+      <c r="N19" t="n">
+        <v>12.85714285714286</v>
+      </c>
+      <c r="P19" t="n">
+        <v>4</v>
+      </c>
+      <c r="T19" t="n">
+        <v>3.508184523809524</v>
+      </c>
+      <c r="U19" t="n">
+        <v>7.280505952380952</v>
+      </c>
+      <c r="V19" t="n">
+        <v>4.585658482142857</v>
+      </c>
+      <c r="W19" t="n">
+        <v>2</v>
+      </c>
+      <c r="X19" t="n">
+        <v>2.405133928571428</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>1.489955357142857</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="inlineStr">
+        <is>
+          <t>Secondary_min_mm</t>
+        </is>
+      </c>
+      <c r="AH19" s="2" t="n">
+        <v>3.818243117559524</v>
       </c>
     </row>
     <row r="20">
@@ -1280,35 +2095,73 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>coronal</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>6.413444378346223</v>
+        <v>2444.671201814059</v>
       </c>
       <c r="D20" t="n">
-        <v>14.80450833134535</v>
+        <v>289.0404007548377</v>
       </c>
       <c r="E20" t="n">
-        <v>11.46418354278658</v>
+        <v>223.8245358353569</v>
       </c>
       <c r="F20" t="n">
-        <v>1.291370491068294</v>
+        <v>1.291370491068293</v>
       </c>
       <c r="G20" t="n">
-        <v>0.367716585865571</v>
+        <v>0.3677165858655712</v>
       </c>
       <c r="H20" t="n">
+        <v>8</v>
+      </c>
+      <c r="I20" t="n">
+        <v>1.915922619047619</v>
+      </c>
+      <c r="J20" t="n">
+        <v>16.96428571428571</v>
+      </c>
+      <c r="K20" t="n">
+        <v>6.878720238095238</v>
+      </c>
+      <c r="L20" t="n">
         <v>2</v>
       </c>
-      <c r="I20" t="n">
-        <v>0.6585365853658537</v>
-      </c>
-      <c r="J20" t="n">
-        <v>0.8689024390243902</v>
-      </c>
-      <c r="K20" t="n">
-        <v>0.7637195121951219</v>
+      <c r="M20" t="n">
+        <v>16.96428571428571</v>
+      </c>
+      <c r="N20" t="n">
+        <v>12.85714285714286</v>
+      </c>
+      <c r="P20" t="n">
+        <v>5</v>
+      </c>
+      <c r="T20" t="n">
+        <v>3.508184523809524</v>
+      </c>
+      <c r="U20" t="n">
+        <v>7.697172619047619</v>
+      </c>
+      <c r="V20" t="n">
+        <v>4.658482142857143</v>
+      </c>
+      <c r="W20" t="n">
+        <v>1</v>
+      </c>
+      <c r="X20" t="n">
+        <v>1.915922619047619</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="inlineStr">
+        <is>
+          <t>Secondary_max_mm</t>
+        </is>
+      </c>
+      <c r="AH20" s="2" t="n">
+        <v>8.40390159970238</v>
       </c>
     </row>
     <row r="21">
@@ -1319,35 +2172,73 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>coronal</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>6.299821534800714</v>
+        <v>2401.360544217687</v>
       </c>
       <c r="D21" t="n">
-        <v>14.70694736155068</v>
+        <v>287.1356389636085</v>
       </c>
       <c r="E21" t="n">
-        <v>11.30600595183489</v>
+        <v>220.7363066786811</v>
       </c>
       <c r="F21" t="n">
         <v>1.300808386640186</v>
       </c>
       <c r="G21" t="n">
-        <v>0.3660100703351644</v>
+        <v>0.3660100703351645</v>
       </c>
       <c r="H21" t="n">
+        <v>8</v>
+      </c>
+      <c r="I21" t="n">
+        <v>1.841517857142857</v>
+      </c>
+      <c r="J21" t="n">
+        <v>16.953125</v>
+      </c>
+      <c r="K21" t="n">
+        <v>6.672479538690475</v>
+      </c>
+      <c r="L21" t="n">
         <v>2</v>
       </c>
-      <c r="I21" t="n">
-        <v>0.6265243902439025</v>
-      </c>
-      <c r="J21" t="n">
-        <v>0.8683307926829269</v>
-      </c>
-      <c r="K21" t="n">
-        <v>0.7474275914634148</v>
+      <c r="M21" t="n">
+        <v>16.953125</v>
+      </c>
+      <c r="N21" t="n">
+        <v>12.23214285714286</v>
+      </c>
+      <c r="P21" t="n">
+        <v>5</v>
+      </c>
+      <c r="T21" t="n">
+        <v>3.355654761904762</v>
+      </c>
+      <c r="U21" t="n">
+        <v>8.139880952380953</v>
+      </c>
+      <c r="V21" t="n">
+        <v>4.470610119047619</v>
+      </c>
+      <c r="W21" t="n">
+        <v>1</v>
+      </c>
+      <c r="X21" t="n">
+        <v>1.841517857142857</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="inlineStr">
+        <is>
+          <t>Secondary_mean_mm</t>
+        </is>
+      </c>
+      <c r="AH21" s="2" t="n">
+        <v>5.383428664434524</v>
       </c>
     </row>
     <row r="22">
@@ -1357,7 +2248,15 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.02439024390243903</v>
+        <v>0.4761904761904762</v>
+      </c>
+      <c r="AG22" t="inlineStr">
+        <is>
+          <t>Tertiary_count</t>
+        </is>
+      </c>
+      <c r="AH22" s="2" t="n">
+        <v>2.75</v>
       </c>
     </row>
     <row r="23">
@@ -1371,6 +2270,14 @@
           <t>mm</t>
         </is>
       </c>
+      <c r="AG23" t="inlineStr">
+        <is>
+          <t>Tertiary_v1_mm</t>
+        </is>
+      </c>
+      <c r="AH23" s="2" t="n">
+        <v>2.569056919642857</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1380,6 +2287,90 @@
       </c>
       <c r="B24" t="n">
         <v>25</v>
+      </c>
+      <c r="AG24" t="inlineStr">
+        <is>
+          <t>Tertiary_v2_mm</t>
+        </is>
+      </c>
+      <c r="AH24" s="2" t="n">
+        <v>1.998299319727891</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>ScalebarMeasuredPixels:</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>42</v>
+      </c>
+      <c r="AG25" t="inlineStr">
+        <is>
+          <t>Tertiary_v3_mm</t>
+        </is>
+      </c>
+      <c r="AH25" s="2" t="n">
+        <v>1.692088293650793</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>ScalebarRealWorldLength:</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>20</v>
+      </c>
+      <c r="AG26" t="inlineStr">
+        <is>
+          <t>Tertiary_min_mm</t>
+        </is>
+      </c>
+      <c r="AH26" s="2" t="n">
+        <v>1.530877976190476</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>ScalebarRealWorldUnit:</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>mm</t>
+        </is>
+      </c>
+      <c r="AG27" t="inlineStr">
+        <is>
+          <t>Tertiary_max_mm</t>
+        </is>
+      </c>
+      <c r="AH27" s="2" t="n">
+        <v>2.785993303571428</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="AG28" t="inlineStr">
+        <is>
+          <t>Tertiary_mean_mm</t>
+        </is>
+      </c>
+      <c r="AH28" s="2" t="n">
+        <v>2.117280505952381</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="AG29" t="inlineStr">
+        <is>
+          <t>Unclassified_count</t>
+        </is>
+      </c>
+      <c r="AH29" s="2" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/measurements/32/Filled_2D_sections/coronal/week32_coronal_Batch_Allmarks.xlsx
+++ b/measurements/32/Filled_2D_sections/coronal/week32_coronal_Batch_Allmarks.xlsx
@@ -8,6 +8,7 @@
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Analysis" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -137,6 +138,211 @@
     </indexedColors>
   </colors>
 </styleSheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>15</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="4953000" cy="3429000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>15</col>
+      <colOff>0</colOff>
+      <row>23</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="4953000" cy="3429000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="2" name="Image 2" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>15</col>
+      <colOff>0</colOff>
+      <row>45</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="4953000" cy="3429000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="3" name="Image 3" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>15</col>
+      <colOff>0</colOff>
+      <row>67</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="4953000" cy="3429000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="4" name="Image 4" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId4"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>24</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="4953000" cy="3429000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="5" name="Image 5" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId5"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>24</col>
+      <colOff>0</colOff>
+      <row>23</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="4953000" cy="3429000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="6" name="Image 6" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId6"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>24</col>
+      <colOff>0</colOff>
+      <row>45</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="4953000" cy="3429000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="7" name="Image 7" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId7"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>35</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="5905500" cy="3429000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="8" name="Image 8" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId8"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2376,4 +2582,1277 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K51"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Workbook Analysis</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Workbook</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>week32_coronal_Batch_Allmarks.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Week</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Axis</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>coronal</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Slice rows analyzed</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Note</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>When a sulcus class count exceeds 3, approximate raw sulcus values are reconstructed from count + min/max/mean for summary stats and boxplots.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Core Metric Summary</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>metric</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>mean</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>std</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>min</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>max</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>area</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>20</v>
+      </c>
+      <c r="C10" t="n">
+        <v>2530.544217687075</v>
+      </c>
+      <c r="D10" t="n">
+        <v>46.12573645116465</v>
+      </c>
+      <c r="E10" t="n">
+        <v>2401.360544217687</v>
+      </c>
+      <c r="F10" t="n">
+        <v>2580.952380952381</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>perimeter</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>20</v>
+      </c>
+      <c r="C11" t="n">
+        <v>309.8390503837948</v>
+      </c>
+      <c r="D11" t="n">
+        <v>20.77494630472225</v>
+      </c>
+      <c r="E11" t="n">
+        <v>281.4015297662644</v>
+      </c>
+      <c r="F11" t="n">
+        <v>346.7049019109635</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>LGI</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>20</v>
+      </c>
+      <c r="C12" t="n">
+        <v>1.374013985534746</v>
+      </c>
+      <c r="D12" t="n">
+        <v>0.08879770933541987</v>
+      </c>
+      <c r="E12" t="n">
+        <v>1.251005288946927</v>
+      </c>
+      <c r="F12" t="n">
+        <v>1.525309215275862</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Compactness</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>20</v>
+      </c>
+      <c r="C13" t="n">
+        <v>0.3350900967180895</v>
+      </c>
+      <c r="D13" t="n">
+        <v>0.04118746531467266</v>
+      </c>
+      <c r="E13" t="n">
+        <v>0.2616744816400987</v>
+      </c>
+      <c r="F13" t="n">
+        <v>0.3937270303097075</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Rounded Sulcus Counts Per Slice</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>File</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Sulci_count</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Primary_count</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Secondary_count</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Tertiary_count</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Unclassified_count</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Sulci_count_rounded</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Primary_count_rounded</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>Secondary_count_rounded</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>Tertiary_count_rounded</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>Unclassified_count_rounded</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>band_axis1_s00_idx0118.png</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>10</v>
+      </c>
+      <c r="C17" t="n">
+        <v>2</v>
+      </c>
+      <c r="D17" t="n">
+        <v>4</v>
+      </c>
+      <c r="E17" t="n">
+        <v>4</v>
+      </c>
+      <c r="F17" t="n">
+        <v>0</v>
+      </c>
+      <c r="G17" t="n">
+        <v>10</v>
+      </c>
+      <c r="H17" t="n">
+        <v>2</v>
+      </c>
+      <c r="I17" t="n">
+        <v>4</v>
+      </c>
+      <c r="J17" t="n">
+        <v>4</v>
+      </c>
+      <c r="K17" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>band_axis1_s01_idx0119.png</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>9</v>
+      </c>
+      <c r="C18" t="n">
+        <v>2</v>
+      </c>
+      <c r="D18" t="n">
+        <v>4</v>
+      </c>
+      <c r="E18" t="n">
+        <v>3</v>
+      </c>
+      <c r="F18" t="n">
+        <v>0</v>
+      </c>
+      <c r="G18" t="n">
+        <v>9</v>
+      </c>
+      <c r="H18" t="n">
+        <v>2</v>
+      </c>
+      <c r="I18" t="n">
+        <v>4</v>
+      </c>
+      <c r="J18" t="n">
+        <v>3</v>
+      </c>
+      <c r="K18" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>band_axis1_s02_idx0120.png</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>8</v>
+      </c>
+      <c r="C19" t="n">
+        <v>2</v>
+      </c>
+      <c r="D19" t="n">
+        <v>3</v>
+      </c>
+      <c r="E19" t="n">
+        <v>3</v>
+      </c>
+      <c r="F19" t="n">
+        <v>0</v>
+      </c>
+      <c r="G19" t="n">
+        <v>8</v>
+      </c>
+      <c r="H19" t="n">
+        <v>2</v>
+      </c>
+      <c r="I19" t="n">
+        <v>3</v>
+      </c>
+      <c r="J19" t="n">
+        <v>3</v>
+      </c>
+      <c r="K19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>band_axis1_s03_idx0122.png</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>10</v>
+      </c>
+      <c r="C20" t="n">
+        <v>3</v>
+      </c>
+      <c r="D20" t="n">
+        <v>3</v>
+      </c>
+      <c r="E20" t="n">
+        <v>4</v>
+      </c>
+      <c r="F20" t="n">
+        <v>0</v>
+      </c>
+      <c r="G20" t="n">
+        <v>10</v>
+      </c>
+      <c r="H20" t="n">
+        <v>3</v>
+      </c>
+      <c r="I20" t="n">
+        <v>3</v>
+      </c>
+      <c r="J20" t="n">
+        <v>4</v>
+      </c>
+      <c r="K20" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>band_axis1_s04_idx0123.png</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>10</v>
+      </c>
+      <c r="C21" t="n">
+        <v>3</v>
+      </c>
+      <c r="D21" t="n">
+        <v>3</v>
+      </c>
+      <c r="E21" t="n">
+        <v>4</v>
+      </c>
+      <c r="F21" t="n">
+        <v>0</v>
+      </c>
+      <c r="G21" t="n">
+        <v>10</v>
+      </c>
+      <c r="H21" t="n">
+        <v>3</v>
+      </c>
+      <c r="I21" t="n">
+        <v>3</v>
+      </c>
+      <c r="J21" t="n">
+        <v>4</v>
+      </c>
+      <c r="K21" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>band_axis1_s05_idx0125.png</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>11</v>
+      </c>
+      <c r="C22" t="n">
+        <v>3</v>
+      </c>
+      <c r="D22" t="n">
+        <v>5</v>
+      </c>
+      <c r="E22" t="n">
+        <v>3</v>
+      </c>
+      <c r="F22" t="n">
+        <v>0</v>
+      </c>
+      <c r="G22" t="n">
+        <v>11</v>
+      </c>
+      <c r="H22" t="n">
+        <v>3</v>
+      </c>
+      <c r="I22" t="n">
+        <v>5</v>
+      </c>
+      <c r="J22" t="n">
+        <v>3</v>
+      </c>
+      <c r="K22" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>band_axis1_s06_idx0126.png</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>11</v>
+      </c>
+      <c r="C23" t="n">
+        <v>3</v>
+      </c>
+      <c r="D23" t="n">
+        <v>5</v>
+      </c>
+      <c r="E23" t="n">
+        <v>3</v>
+      </c>
+      <c r="F23" t="n">
+        <v>0</v>
+      </c>
+      <c r="G23" t="n">
+        <v>11</v>
+      </c>
+      <c r="H23" t="n">
+        <v>3</v>
+      </c>
+      <c r="I23" t="n">
+        <v>5</v>
+      </c>
+      <c r="J23" t="n">
+        <v>3</v>
+      </c>
+      <c r="K23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>band_axis1_s07_idx0127.png</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>10</v>
+      </c>
+      <c r="C24" t="n">
+        <v>2</v>
+      </c>
+      <c r="D24" t="n">
+        <v>5</v>
+      </c>
+      <c r="E24" t="n">
+        <v>3</v>
+      </c>
+      <c r="F24" t="n">
+        <v>0</v>
+      </c>
+      <c r="G24" t="n">
+        <v>10</v>
+      </c>
+      <c r="H24" t="n">
+        <v>2</v>
+      </c>
+      <c r="I24" t="n">
+        <v>5</v>
+      </c>
+      <c r="J24" t="n">
+        <v>3</v>
+      </c>
+      <c r="K24" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>band_axis1_s08_idx0129.png</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>11</v>
+      </c>
+      <c r="C25" t="n">
+        <v>2</v>
+      </c>
+      <c r="D25" t="n">
+        <v>5</v>
+      </c>
+      <c r="E25" t="n">
+        <v>4</v>
+      </c>
+      <c r="F25" t="n">
+        <v>0</v>
+      </c>
+      <c r="G25" t="n">
+        <v>11</v>
+      </c>
+      <c r="H25" t="n">
+        <v>2</v>
+      </c>
+      <c r="I25" t="n">
+        <v>5</v>
+      </c>
+      <c r="J25" t="n">
+        <v>4</v>
+      </c>
+      <c r="K25" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>band_axis1_s09_idx0130.png</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>10</v>
+      </c>
+      <c r="C26" t="n">
+        <v>2</v>
+      </c>
+      <c r="D26" t="n">
+        <v>5</v>
+      </c>
+      <c r="E26" t="n">
+        <v>3</v>
+      </c>
+      <c r="F26" t="n">
+        <v>0</v>
+      </c>
+      <c r="G26" t="n">
+        <v>10</v>
+      </c>
+      <c r="H26" t="n">
+        <v>2</v>
+      </c>
+      <c r="I26" t="n">
+        <v>5</v>
+      </c>
+      <c r="J26" t="n">
+        <v>3</v>
+      </c>
+      <c r="K26" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>band_axis1_s10_idx0132.png</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>9</v>
+      </c>
+      <c r="C27" t="n">
+        <v>2</v>
+      </c>
+      <c r="D27" t="n">
+        <v>4</v>
+      </c>
+      <c r="E27" t="n">
+        <v>3</v>
+      </c>
+      <c r="F27" t="n">
+        <v>0</v>
+      </c>
+      <c r="G27" t="n">
+        <v>9</v>
+      </c>
+      <c r="H27" t="n">
+        <v>2</v>
+      </c>
+      <c r="I27" t="n">
+        <v>4</v>
+      </c>
+      <c r="J27" t="n">
+        <v>3</v>
+      </c>
+      <c r="K27" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>band_axis1_s11_idx0133.png</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>9</v>
+      </c>
+      <c r="C28" t="n">
+        <v>3</v>
+      </c>
+      <c r="D28" t="n">
+        <v>3</v>
+      </c>
+      <c r="E28" t="n">
+        <v>3</v>
+      </c>
+      <c r="F28" t="n">
+        <v>0</v>
+      </c>
+      <c r="G28" t="n">
+        <v>9</v>
+      </c>
+      <c r="H28" t="n">
+        <v>3</v>
+      </c>
+      <c r="I28" t="n">
+        <v>3</v>
+      </c>
+      <c r="J28" t="n">
+        <v>3</v>
+      </c>
+      <c r="K28" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>band_axis1_s12_idx0135.png</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
+        <v>9</v>
+      </c>
+      <c r="C29" t="n">
+        <v>2</v>
+      </c>
+      <c r="D29" t="n">
+        <v>5</v>
+      </c>
+      <c r="E29" t="n">
+        <v>2</v>
+      </c>
+      <c r="F29" t="n">
+        <v>0</v>
+      </c>
+      <c r="G29" t="n">
+        <v>9</v>
+      </c>
+      <c r="H29" t="n">
+        <v>2</v>
+      </c>
+      <c r="I29" t="n">
+        <v>5</v>
+      </c>
+      <c r="J29" t="n">
+        <v>2</v>
+      </c>
+      <c r="K29" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>band_axis1_s13_idx0136.png</t>
+        </is>
+      </c>
+      <c r="B30" t="n">
+        <v>9</v>
+      </c>
+      <c r="C30" t="n">
+        <v>2</v>
+      </c>
+      <c r="D30" t="n">
+        <v>4</v>
+      </c>
+      <c r="E30" t="n">
+        <v>3</v>
+      </c>
+      <c r="F30" t="n">
+        <v>0</v>
+      </c>
+      <c r="G30" t="n">
+        <v>9</v>
+      </c>
+      <c r="H30" t="n">
+        <v>2</v>
+      </c>
+      <c r="I30" t="n">
+        <v>4</v>
+      </c>
+      <c r="J30" t="n">
+        <v>3</v>
+      </c>
+      <c r="K30" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>band_axis1_s14_idx0137.png</t>
+        </is>
+      </c>
+      <c r="B31" t="n">
+        <v>8</v>
+      </c>
+      <c r="C31" t="n">
+        <v>2</v>
+      </c>
+      <c r="D31" t="n">
+        <v>4</v>
+      </c>
+      <c r="E31" t="n">
+        <v>2</v>
+      </c>
+      <c r="F31" t="n">
+        <v>0</v>
+      </c>
+      <c r="G31" t="n">
+        <v>8</v>
+      </c>
+      <c r="H31" t="n">
+        <v>2</v>
+      </c>
+      <c r="I31" t="n">
+        <v>4</v>
+      </c>
+      <c r="J31" t="n">
+        <v>2</v>
+      </c>
+      <c r="K31" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>band_axis1_s15_idx0139.png</t>
+        </is>
+      </c>
+      <c r="B32" t="n">
+        <v>8</v>
+      </c>
+      <c r="C32" t="n">
+        <v>2</v>
+      </c>
+      <c r="D32" t="n">
+        <v>4</v>
+      </c>
+      <c r="E32" t="n">
+        <v>2</v>
+      </c>
+      <c r="F32" t="n">
+        <v>0</v>
+      </c>
+      <c r="G32" t="n">
+        <v>8</v>
+      </c>
+      <c r="H32" t="n">
+        <v>2</v>
+      </c>
+      <c r="I32" t="n">
+        <v>4</v>
+      </c>
+      <c r="J32" t="n">
+        <v>2</v>
+      </c>
+      <c r="K32" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>band_axis1_s16_idx0140.png</t>
+        </is>
+      </c>
+      <c r="B33" t="n">
+        <v>8</v>
+      </c>
+      <c r="C33" t="n">
+        <v>2</v>
+      </c>
+      <c r="D33" t="n">
+        <v>4</v>
+      </c>
+      <c r="E33" t="n">
+        <v>2</v>
+      </c>
+      <c r="F33" t="n">
+        <v>0</v>
+      </c>
+      <c r="G33" t="n">
+        <v>8</v>
+      </c>
+      <c r="H33" t="n">
+        <v>2</v>
+      </c>
+      <c r="I33" t="n">
+        <v>4</v>
+      </c>
+      <c r="J33" t="n">
+        <v>2</v>
+      </c>
+      <c r="K33" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>band_axis1_s17_idx0142.png</t>
+        </is>
+      </c>
+      <c r="B34" t="n">
+        <v>8</v>
+      </c>
+      <c r="C34" t="n">
+        <v>2</v>
+      </c>
+      <c r="D34" t="n">
+        <v>4</v>
+      </c>
+      <c r="E34" t="n">
+        <v>2</v>
+      </c>
+      <c r="F34" t="n">
+        <v>0</v>
+      </c>
+      <c r="G34" t="n">
+        <v>8</v>
+      </c>
+      <c r="H34" t="n">
+        <v>2</v>
+      </c>
+      <c r="I34" t="n">
+        <v>4</v>
+      </c>
+      <c r="J34" t="n">
+        <v>2</v>
+      </c>
+      <c r="K34" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>band_axis1_s18_idx0143.png</t>
+        </is>
+      </c>
+      <c r="B35" t="n">
+        <v>8</v>
+      </c>
+      <c r="C35" t="n">
+        <v>2</v>
+      </c>
+      <c r="D35" t="n">
+        <v>5</v>
+      </c>
+      <c r="E35" t="n">
+        <v>1</v>
+      </c>
+      <c r="F35" t="n">
+        <v>0</v>
+      </c>
+      <c r="G35" t="n">
+        <v>8</v>
+      </c>
+      <c r="H35" t="n">
+        <v>2</v>
+      </c>
+      <c r="I35" t="n">
+        <v>5</v>
+      </c>
+      <c r="J35" t="n">
+        <v>1</v>
+      </c>
+      <c r="K35" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>band_axis1_s19_idx0144.png</t>
+        </is>
+      </c>
+      <c r="B36" t="n">
+        <v>8</v>
+      </c>
+      <c r="C36" t="n">
+        <v>2</v>
+      </c>
+      <c r="D36" t="n">
+        <v>5</v>
+      </c>
+      <c r="E36" t="n">
+        <v>1</v>
+      </c>
+      <c r="F36" t="n">
+        <v>0</v>
+      </c>
+      <c r="G36" t="n">
+        <v>8</v>
+      </c>
+      <c r="H36" t="n">
+        <v>2</v>
+      </c>
+      <c r="I36" t="n">
+        <v>5</v>
+      </c>
+      <c r="J36" t="n">
+        <v>1</v>
+      </c>
+      <c r="K36" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Rounded Sulcus Count Summary</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>metric</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>mean</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>std</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>min</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>max</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Sulci_count_rounded</t>
+        </is>
+      </c>
+      <c r="B40" t="n">
+        <v>20</v>
+      </c>
+      <c r="C40" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="D40" t="n">
+        <v>1.105012502906165</v>
+      </c>
+      <c r="E40" t="n">
+        <v>8</v>
+      </c>
+      <c r="F40" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Primary_count_rounded</t>
+        </is>
+      </c>
+      <c r="B41" t="n">
+        <v>20</v>
+      </c>
+      <c r="C41" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="D41" t="n">
+        <v>0.4442616583193193</v>
+      </c>
+      <c r="E41" t="n">
+        <v>2</v>
+      </c>
+      <c r="F41" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Secondary_count_rounded</t>
+        </is>
+      </c>
+      <c r="B42" t="n">
+        <v>20</v>
+      </c>
+      <c r="C42" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="D42" t="n">
+        <v>0.7677718959499146</v>
+      </c>
+      <c r="E42" t="n">
+        <v>3</v>
+      </c>
+      <c r="F42" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Tertiary_count_rounded</t>
+        </is>
+      </c>
+      <c r="B43" t="n">
+        <v>20</v>
+      </c>
+      <c r="C43" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="D43" t="n">
+        <v>0.910465468000326</v>
+      </c>
+      <c r="E43" t="n">
+        <v>1</v>
+      </c>
+      <c r="F43" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Unclassified_count_rounded</t>
+        </is>
+      </c>
+      <c r="B44" t="n">
+        <v>20</v>
+      </c>
+      <c r="C44" t="n">
+        <v>0</v>
+      </c>
+      <c r="D44" t="n">
+        <v>0</v>
+      </c>
+      <c r="E44" t="n">
+        <v>0</v>
+      </c>
+      <c r="F44" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Sulcus Value Summary</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>metric</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>mean</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>std</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>min</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>max</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>primary_sulcus_values</t>
+        </is>
+      </c>
+      <c r="B48" t="n">
+        <v>45</v>
+      </c>
+      <c r="C48" t="n">
+        <v>14.52083333333333</v>
+      </c>
+      <c r="D48" t="n">
+        <v>2.496215888011752</v>
+      </c>
+      <c r="E48" t="n">
+        <v>10.65290178571428</v>
+      </c>
+      <c r="F48" t="n">
+        <v>20.17857142857143</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>secondary_sulcus_values</t>
+        </is>
+      </c>
+      <c r="B49" t="n">
+        <v>84</v>
+      </c>
+      <c r="C49" t="n">
+        <v>5.438478776927437</v>
+      </c>
+      <c r="D49" t="n">
+        <v>1.875180742101909</v>
+      </c>
+      <c r="E49" t="n">
+        <v>3.322172619047619</v>
+      </c>
+      <c r="F49" t="n">
+        <v>9.047619047619047</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>tertiary_sulcus_values</t>
+        </is>
+      </c>
+      <c r="B50" t="n">
+        <v>55</v>
+      </c>
+      <c r="C50" t="n">
+        <v>2.148843344155845</v>
+      </c>
+      <c r="D50" t="n">
+        <v>0.6833271879047168</v>
+      </c>
+      <c r="E50" t="n">
+        <v>0.9951636904761905</v>
+      </c>
+      <c r="F50" t="n">
+        <v>3.37797619047619</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>unclassified_sulcus_values</t>
+        </is>
+      </c>
+      <c r="B51" t="n">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing r:id="rId1"/>
+</worksheet>
 </file>